--- a/target/classes/Exceldata/Data.xlsx
+++ b/target/classes/Exceldata/Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\atmaurya\eclipse-workspace\Module-Consult\src\test\resources\Exceldata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{65F17B7D-FFB8-4535-84E9-6E1D20CC7B34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51DD7595-A2FE-4766-8597-DD327963D470}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{36EBAE0D-1C44-419C-A15F-E7BA5B11CA27}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="10">
   <si>
     <t>VaildSearchQuery</t>
   </si>
@@ -54,6 +54,18 @@
   </si>
   <si>
     <t>Heart</t>
+  </si>
+  <si>
+    <t>Perplexity</t>
+  </si>
+  <si>
+    <t>tag</t>
+  </si>
+  <si>
+    <t>Delhi</t>
+  </si>
+  <si>
+    <t>Charbag</t>
   </si>
 </sst>
 </file>
@@ -425,7 +437,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68CE0E31-3723-4C17-913F-5BF1314869F2}">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="22.6328125" customWidth="1"/>
@@ -444,20 +456,40 @@
       <c r="A2" t="s">
         <v>1</v>
       </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>2</v>
       </c>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
